--- a/rates/linkport-rate-sheet.xlsx
+++ b/rates/linkport-rate-sheet.xlsx
@@ -32,13 +32,13 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2026-06-v1</t>
+    <t>2026-10-v1</t>
   </si>
   <si>
     <t>Valid through</t>
   </si>
   <si>
-    <t>2026-06-30</t>
+    <t>2026-12-31</t>
   </si>
   <si>
     <t>Kind</t>
